--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_xgb_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_xgb_quarterly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>1.206580663011472</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1040,51 +1041,51 @@
         <v>0.798509113087996</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1189,51 +1190,51 @@
         <v>0.8860681916838462</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1342,59 +1343,59 @@
         <v>0.798509113087996</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR6" s="3" t="n">
@@ -1402,15 +1403,15 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
     </row>
@@ -1509,51 +1510,51 @@
         <v>1.661920700470786</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1662,43 +1663,43 @@
         <v>1.212304031065877</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
@@ -1706,31 +1707,31 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -1829,51 +1830,51 @@
         <v>0.7423984269578163</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1982,75 +1983,75 @@
         <v>1.109142987618174</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AR10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -2349,66 +2350,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.09032004823014436</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.04076898034342898</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582908825</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493455</v>
+        <v>0.2044255219913531</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2456,34 +2459,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>38980</v>
+        <v>36104</v>
       </c>
       <c r="M3" t="n">
-        <v>1632</v>
+        <v>78</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.4742034398605798</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="P3" t="n">
-        <v>1628</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.2108530619377716</v>
+        <v>0.09396824967670085</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.1956317496068602</v>
+        <v>0.04041855151300761</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -2493,29 +2496,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.4742034398605798</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>994</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.9018762689030144</v>
+        <v>0.2148104911130229</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2571,34 +2576,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>38012</v>
+        <v>36104</v>
       </c>
       <c r="M4" t="n">
-        <v>963</v>
+        <v>78</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="P4" t="n">
-        <v>813</v>
+        <v>77</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1378626392028849</v>
+        <v>0.08652899115469197</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0982768979428859</v>
+        <v>0.03721870417281659</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2608,38 +2613,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>380</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4140787579868381</v>
+        <v>0.1932346188529419</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.09735485166397427</v>
+        <v>-0.003199847340191027</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1813776296657191</v>
+        <v>0.01488449085184429</v>
       </c>
       <c r="AH4" t="n">
-        <v>-614</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -2694,34 +2701,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36880</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>38842</v>
+        <v>36510</v>
       </c>
       <c r="M5" t="n">
-        <v>1537</v>
+        <v>358</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1715675340948265</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1761854474856462</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="P5" t="n">
-        <v>1533</v>
+        <v>356</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1091551197830182</v>
+        <v>0.1147501641520448</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.09828531023595014</v>
+        <v>0.1052171665462235</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2731,38 +2738,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>189</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-449</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1715675340948265</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1761854474856462</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1348</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>272</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2070989985977505</v>
+        <v>0.2148104911130229</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.09734643937091003</v>
+        <v>0.06479861503321591</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3026359057657533</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>354</v>
+        <v>280</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2821,34 +2830,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>38986</v>
+        <v>36105</v>
       </c>
       <c r="M6" t="n">
-        <v>1636</v>
+        <v>79</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.4013690155818542</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4047059514853544</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="P6" t="n">
-        <v>1632</v>
+        <v>77</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1856319150306758</v>
+        <v>0.09207043045792021</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1724421064351888</v>
+        <v>0.0398521016690362</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -2858,50 +2867,52 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4013690155818542</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4047059514853544</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1053</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0.2148104911130229</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.0005664498439714102</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1</v>
       </c>
-      <c r="AE6" s="3" t="n">
-        <v>0.6704781844394085</v>
-      </c>
-      <c r="AF6" s="3" t="n">
-        <v>-0.02318964317167138</v>
-      </c>
-      <c r="AG6" s="3" t="n">
-        <v>0.07283442427872555</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>59</v>
-      </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.07416520849230289</v>
+        <v>0.002633397496219617</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.1085432053869936</v>
+        <v>-0.01488449085184429</v>
       </c>
       <c r="AL6" t="n">
-        <v>673</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -2952,76 +2963,80 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37691</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>36258</v>
+      </c>
       <c r="M7" t="n">
-        <v>1896</v>
+        <v>182</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.6222255887591961</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.6243314085866118</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="P7" t="n">
-        <v>1893</v>
+        <v>180</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.4113072634183547</v>
+        <v>0.1085951754058021</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.4113072634183547</v>
+        <v>0.071092230200585</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.2459662486835871</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>742</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>-0.1768263384984526</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>-0.1804907434017395</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>151</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>96</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0.2148104911130229</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>0.03067367868757739</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>104</v>
       </c>
-      <c r="Y7" s="3" t="n">
-        <v>-0.6222255887591961</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>-0.6243314085866118</v>
-      </c>
-      <c r="AA7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1154</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="3" t="n">
-        <v>1.647082412796277</v>
-      </c>
-      <c r="AF7" s="3" t="n">
-        <v>0.2156755138114946</v>
-      </c>
-      <c r="AG7" s="3" t="n">
-        <v>-0.1480221488986163</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -3077,86 +3092,92 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>36105</v>
+      </c>
       <c r="M8" t="n">
-        <v>1896</v>
+        <v>79</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.545448766865211</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.5479825620901642</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="P8" t="n">
-        <v>1893</v>
+        <v>77</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.3094726277498512</v>
+        <v>0.09207043045792021</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.3094726277498512</v>
+        <v>0.0398521016690362</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>31</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.1768263384984526</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>-0.1804907434017395</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.2148104911130229</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.0005664498439714102</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>-0.06735016957990425</v>
-      </c>
-      <c r="W8" t="n">
-        <v>638</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>-0.545448766865211</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>-0.5479825620901642</v>
-      </c>
-      <c r="AA8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="b">
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>0.002633397496219617</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>-0.01488449085184429</v>
+      </c>
+      <c r="AL8" t="n">
         <v>1</v>
       </c>
-      <c r="AE8" s="3" t="n">
-        <v>1.199972031983175</v>
-      </c>
-      <c r="AF8" s="3" t="n">
-        <v>0.113840878142991</v>
-      </c>
-      <c r="AG8" s="3" t="n">
-        <v>-0.07124532700463126</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.2111957298069653</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.2526229566703504</v>
-      </c>
-      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
@@ -3204,83 +3225,87 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>37438</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>1896</v>
+        <v>90</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.402820538083003</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.4260784533960039</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1844</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.2796548066821187</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.2796548066821187</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.06539812531811628</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-70</v>
+        <v>-31</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.402820538083003</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.4260784533960039</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1328</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.6745384993481101</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.08402305707525851</v>
+        <v>-0.04041855151300761</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.07138290177757678</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.1768263384984526</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-47</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.05783218662559397</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.05280264614878494</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3329,34 +3354,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>39344</v>
+        <v>36104</v>
       </c>
       <c r="M10" t="n">
-        <v>1882</v>
+        <v>78</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.5157200702869663</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.5258737762823344</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="P10" t="n">
-        <v>1861</v>
+        <v>77</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.2664561432239907</v>
+        <v>0.08652899115469197</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.2654710894150666</v>
+        <v>0.03721870417281659</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -3366,56 +3391,62 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X10" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.5157200702869663</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.5258737762823344</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1299</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>1.064921419709801</v>
+        <v>0.1932346188529419</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.06983933980820642</v>
+        <v>-0.003199847340191027</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>-0.04151663042638654</v>
+        <v>0.01488449085184429</v>
       </c>
       <c r="AH10" t="n">
-        <v>305</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.1671941914721807</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.2228942600921057</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>919</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="n">
+        <v>0.05783218662559397</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>-0.01680153018289654</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3712,68 +3743,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.5035092528573126</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286764</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2354171526922728</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1562892258388244</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459472</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616542</v>
+        <v>0.94639982458421</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3821,34 +3850,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>38980</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1631</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.4746076449481669</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.4771343763893187</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1628</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.2109176516350861</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1956833334573563</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>41137</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1224</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.5468101317287759</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.5468101317287759</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1223</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.231793989333857</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1544522944008473</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -3858,31 +3887,29 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4746076449481669</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4771343763893187</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>869</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9</v>
-      </c>
+        <v>994</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.206580663011473</v>
+        <v>0.9033394574257632</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3938,34 +3965,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>38007</v>
+      </c>
+      <c r="M4" t="n">
+        <v>959</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.291230325563591</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.3309499985899496</v>
+      </c>
+      <c r="P4" t="n">
+        <v>796</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1381187240689723</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09828087349740594</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40746</v>
-      </c>
-      <c r="M4" t="n">
-        <v>954</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="P4" t="n">
-        <v>953</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1982156637126214</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.1166175213781546</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3975,40 +4002,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.291230325563591</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>599</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-261</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>0.410895578729674</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.03783477302269261</v>
+        <v>-0.09740245995995039</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1028262190106605</v>
+        <v>0.1833773193845759</v>
       </c>
       <c r="AH4" t="n">
-        <v>-270</v>
+        <v>-617</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4063,34 +4088,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>36880</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>38842</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1536</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1722043899490231</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1761854474856462</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1533</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1091906231567927</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.09831122594114308</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>41061</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>41411</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1411</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.2320220775021999</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2597750654112301</v>
-      </c>
-      <c r="P5" t="n">
-        <v>486</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.09874646737215202</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.07064201293787455</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4100,40 +4125,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1171</v>
+        <v>188</v>
       </c>
       <c r="X5" t="n">
-        <v>816</v>
+        <v>-449</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2320220775021999</v>
+        <v>-0.1722043899490231</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2597750654112301</v>
+        <v>-0.1761854474856462</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>240</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-620</v>
-      </c>
+        <v>1348</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.3021207650703848</v>
+        <v>0.2080276675282422</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.08381028146297272</v>
+        <v>-0.09737210751621325</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.314788054226576</v>
+        <v>0.3024032549991438</v>
       </c>
       <c r="AH5" t="n">
-        <v>-629</v>
+        <v>354</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4142,12 +4165,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.1265041286974922</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.0912732381757877</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4196,34 +4215,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>38986</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1635</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.4018292119920874</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.4047059514853544</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1632</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1856886398341482</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1724875756796006</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>41130</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1219</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1218</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1837653158688263</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1221989883475345</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -4233,62 +4252,56 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.4018292119920874</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.4047059514853544</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>864</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4</v>
-      </c>
+        <v>1053</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>0.671763349277384</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.03225330605331281</v>
+        <v>-0.0231957577777557</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1028262190106605</v>
+        <v>0.07277843295607944</v>
       </c>
       <c r="AH6" t="n">
-        <v>-5</v>
+        <v>59</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.005581466969379806</v>
+        <v>0.07420670218219469</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0</v>
+        <v>-0.1105988864284965</v>
       </c>
       <c r="AL6" t="n">
-        <v>265</v>
+        <v>676</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.1265041286974922</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.002061632408944414</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4333,80 +4346,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37691</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.6225160021064103</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.6243314085866118</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.4114157162253598</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.4114157162253598</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40101</v>
-      </c>
-      <c r="M7" t="n">
-        <v>509</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3235130044559731</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3235130044559731</v>
-      </c>
-      <c r="P7" t="n">
-        <v>508</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1142755179490045</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.04913177294975803</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.2465459106699907</v>
+      </c>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>741</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3235130044559731</v>
+        <v>-0.6225160021064103</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3235130044559731</v>
+        <v>-0.6243314085866118</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>154</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-706</v>
-      </c>
+        <v>1154</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4782250162781116</v>
+        <v>1.649118917835276</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.1053205214510892</v>
+        <v>0.2157323827680034</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2232971272728028</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-715</v>
-      </c>
+        <v>-0.1479083571582435</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -4462,92 +4471,86 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.5457982022456049</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.5479825620901643</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.3095542289715067</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.3095542289715067</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>41165</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1243</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.4853919564080009</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.4853919564080009</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1242</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1941196178146122</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1303478185962128</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.06806714233129163</v>
+      </c>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4853919564080009</v>
+        <v>-0.5457982022456049</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4853919564080009</v>
+        <v>-0.5479825620901643</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>888</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>28</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.9432265244435982</v>
+        <v>1.201664557348889</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.02410447580463443</v>
+        <v>0.1138708955141504</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.06141817532077498</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>19</v>
-      </c>
+        <v>-0.07119055729743806</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.01373029721805819</v>
+        <v>0.2112733554741008</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.04140804368988549</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>289</v>
-      </c>
+        <v>-0.254567876682014</v>
+      </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
@@ -4595,80 +4598,76 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37438</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.4032796186381237</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.4260784533960038</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1846</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.2797285455908971</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.2797285455908971</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>40911</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>41374</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1384</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.1668689912746076</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2272156375034153</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1205</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1146364550721955</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.08122164559287288</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.06611659869975028</v>
+      </c>
       <c r="W9" t="n">
-        <v>1067</v>
+        <v>567</v>
       </c>
       <c r="X9" t="n">
-        <v>712</v>
+        <v>-70</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1668689912746076</v>
+        <v>-0.4032796186381237</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2272156375034153</v>
+        <v>-0.4260784533960038</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>317</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-543</v>
-      </c>
+        <v>1328</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2002914181887199</v>
+        <v>0.6758267879466948</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.07323064880797438</v>
+        <v>0.08404521213354077</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3799411404541683</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-552</v>
-      </c>
+        <v>0.0713280263100432</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -4724,34 +4723,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>39344</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1881</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.5160923595452955</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.5258737762823346</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1862</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.2665269245091346</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.2655410883851467</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>41117</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1210</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4592803435105396</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4592803435105396</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1209</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2039069967224262</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.135091601252573</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -4761,52 +4760,50 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.4592803435105396</v>
+        <v>-0.5160923595452955</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.4592803435105396</v>
+        <v>-0.5258737762823346</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>855</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-5</v>
-      </c>
+        <v>1299</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.8493871787320382</v>
+        <v>1.06651004530606</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.01936069314827424</v>
+        <v>0.06985775492779034</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.08752978821823632</v>
+        <v>-0.04148471459712866</v>
       </c>
       <c r="AH10" t="n">
-        <v>-14</v>
+        <v>305</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.01847407987441838</v>
+        <v>0.1672602148877407</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.01529643079242415</v>
+        <v>-0.2248620339817046</v>
       </c>
       <c r="AL10" t="n">
-        <v>256</v>
+        <v>922</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -5109,34 +5106,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.08269444253856398</v>
+        <v>0.2354171526922728</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.05218963375687868</v>
+        <v>0.1563175570682493</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5146,22 +5143,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5170,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160748</v>
+        <v>1.014136226616542</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5218,34 +5215,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43511</v>
+        <v>41137</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>1224</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="P3" t="n">
-        <v>90</v>
+        <v>1223</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.04865286626178858</v>
+        <v>0.231793989333857</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.02598767857457803</v>
+        <v>0.154480292641701</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5255,31 +5252,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>36</v>
+        <v>869</v>
       </c>
       <c r="AC3" t="n">
-        <v>-40</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.1596950545770186</v>
+        <v>1.206580663011473</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -5335,34 +5332,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43542</v>
+        <v>40746</v>
       </c>
       <c r="M4" t="n">
-        <v>120</v>
+        <v>954</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="P4" t="n">
-        <v>116</v>
+        <v>953</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04694464568316091</v>
+        <v>0.1982156637126214</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02744587744229462</v>
+        <v>0.1166386611447342</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -5372,40 +5369,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>56</v>
+        <v>599</v>
       </c>
       <c r="AC4" t="n">
-        <v>-20</v>
+        <v>-261</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1600183179571426</v>
+        <v>0.798509113087996</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.00145819886771659</v>
+        <v>-0.03784163149696679</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>-0.000240296728010847</v>
+        <v>0.1028262190106605</v>
       </c>
       <c r="AH4" t="n">
-        <v>20</v>
+        <v>-270</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5460,34 +5457,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>41061</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43501</v>
+        <v>41411</v>
       </c>
       <c r="M5" t="n">
-        <v>92</v>
+        <v>1411</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1374858172388338</v>
+        <v>-0.2320220775021999</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.2597750654112301</v>
       </c>
       <c r="P5" t="n">
-        <v>77</v>
+        <v>486</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.05035665070842264</v>
+        <v>0.09874646737215202</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.02581051559248221</v>
+        <v>0.0706548185235753</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -5497,40 +5494,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>1171</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1374858172388338</v>
+        <v>-0.2320220775021999</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.2597750654112301</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>28</v>
+        <v>240</v>
       </c>
       <c r="AC5" t="n">
-        <v>-48</v>
+        <v>-620</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1594012249151666</v>
+        <v>0.3021207650703848</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.0001771629820958194</v>
+        <v>-0.08382547411812569</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.000218533527122422</v>
+        <v>0.314788054226576</v>
       </c>
       <c r="AH5" t="n">
-        <v>-8</v>
+        <v>-629</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5540,10 +5537,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.1436226220825925</v>
+        <v>0.1265041286974922</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.117446750589972</v>
+        <v>-0.0912732381757877</v>
       </c>
     </row>
     <row r="6">
@@ -5593,34 +5590,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43516</v>
+        <v>41130</v>
       </c>
       <c r="M6" t="n">
-        <v>102</v>
+        <v>1219</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1424443119205701</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1461625015373461</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="P6" t="n">
-        <v>97</v>
+        <v>1218</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.0482248996287641</v>
+        <v>0.1837653158688263</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.02601287258767963</v>
+        <v>0.122221139890968</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5630,61 +5627,61 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1424443119205701</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1461625015373461</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>38</v>
+        <v>864</v>
       </c>
       <c r="AC6" t="n">
-        <v>-38</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1661050283971486</v>
+        <v>0.798509113087996</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>2.519401310159541e-05</v>
+        <v>-0.03225915275073296</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-0.004739961154613836</v>
+        <v>0.1028262190106605</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>-0.001433004854614995</v>
+        <v>0.005582478746233827</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.004499664426602989</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-18</v>
+        <v>265</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1436226220825925</v>
+        <v>0.1265041286974922</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>0.01922590984037953</v>
+        <v>-0.002061632408944414</v>
       </c>
     </row>
     <row r="7">
@@ -5730,34 +5727,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43763</v>
+        <v>40101</v>
       </c>
       <c r="M7" t="n">
-        <v>275</v>
+        <v>509</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.3235130044559731</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.3235130044559731</v>
       </c>
       <c r="P7" t="n">
-        <v>265</v>
+        <v>508</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.06407021001792397</v>
+        <v>0.1142755179490045</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.05657298021591087</v>
+        <v>0.04914067928046651</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -5767,40 +5764,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.3235130044559731</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.3235130044559731</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="AC7" t="n">
-        <v>135</v>
+        <v>-706</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1596950545770186</v>
+        <v>0.4782250162781116</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.03058530164133284</v>
+        <v>-0.1053396133612345</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0</v>
+        <v>0.2232971272728028</v>
       </c>
       <c r="AH7" t="n">
-        <v>175</v>
+        <v>-715</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5859,34 +5856,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43537</v>
+        <v>41165</v>
       </c>
       <c r="M8" t="n">
-        <v>117</v>
+        <v>1243</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.4853919564080009</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.4853919564080009</v>
       </c>
       <c r="P8" t="n">
-        <v>107</v>
+        <v>1242</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.04968699774135937</v>
+        <v>0.1941196178146122</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.02868680152119817</v>
+        <v>0.1303714473136364</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5896,52 +5893,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.4853919564080009</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.4853919564080009</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>53</v>
+        <v>888</v>
       </c>
       <c r="AC8" t="n">
-        <v>-23</v>
+        <v>28</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1596950545770186</v>
+        <v>0.9432265244435982</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.002699122946620135</v>
+        <v>-0.02410884532806462</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>0.06141817532077498</v>
       </c>
       <c r="AH8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.001240924078903544</v>
+        <v>0.01373278616890217</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>0.000240296728010847</v>
+        <v>-0.04140804368988549</v>
       </c>
       <c r="AL8" t="n">
-        <v>-3</v>
+        <v>289</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -5992,34 +5989,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
+        <v>40911</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43763</v>
+        <v>41374</v>
       </c>
       <c r="M9" t="n">
-        <v>275</v>
+        <v>1384</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.1668689912746076</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1461625015373466</v>
+        <v>-0.2272156375034153</v>
       </c>
       <c r="P9" t="n">
-        <v>265</v>
+        <v>1205</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.06407021001792426</v>
+        <v>0.1146364550721955</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.05657298021591112</v>
+        <v>0.08123636899471465</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -6029,40 +6026,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>1067</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>712</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.1668689912746076</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1461625015373466</v>
+        <v>-0.2272156375034153</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>211</v>
+        <v>317</v>
       </c>
       <c r="AC9" t="n">
-        <v>135</v>
+        <v>-543</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1596950545770186</v>
+        <v>0.2002914181887199</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.03058530164133309</v>
+        <v>-0.07324392364698634</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0</v>
+        <v>0.3799411404541683</v>
       </c>
       <c r="AH9" t="n">
-        <v>175</v>
+        <v>-552</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -6121,34 +6118,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>43537</v>
+        <v>41117</v>
       </c>
       <c r="M10" t="n">
-        <v>117</v>
+        <v>1210</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.4592803435105396</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.4592803435105396</v>
       </c>
       <c r="P10" t="n">
-        <v>107</v>
+        <v>1209</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.04968699774135937</v>
+        <v>0.2039069967224262</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.02868680152119817</v>
+        <v>0.1351160898961627</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -6158,52 +6155,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.4592803435105396</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.4592803435105396</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>53</v>
+        <v>855</v>
       </c>
       <c r="AC10" t="n">
-        <v>-23</v>
+        <v>-5</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.1596950545770186</v>
+        <v>0.8493871787320382</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.002699122946620135</v>
+        <v>-0.01936420274553832</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0</v>
+        <v>0.08752978821823632</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>-14</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.001240924078903544</v>
+        <v>0.01847742875142847</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>0.000240296728010847</v>
+        <v>-0.01529643079242415</v>
       </c>
       <c r="AL10" t="n">
-        <v>-3</v>
+        <v>256</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -6506,34 +6503,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606708</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2022979914860072</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428324</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05211846719049073</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425155</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440421</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -6543,22 +6540,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -6567,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320053</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -6615,34 +6612,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43511</v>
+      </c>
+      <c r="M3" t="n">
+        <v>101</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1393233790300028</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1461625015373463</v>
+      </c>
+      <c r="P3" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.04842348838498468</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.02595625199141308</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M3" t="n">
-        <v>122</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="P3" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1335580210897492</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06803515216200837</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -6652,31 +6649,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="AC3" t="n">
-        <v>44</v>
+        <v>-42</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.47136484549988</v>
+        <v>0.1618765697074274</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6732,34 +6729,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43539</v>
+      </c>
+      <c r="M4" t="n">
+        <v>120</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1373591481699221</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1410541034597296</v>
+      </c>
+      <c r="P4" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04694462358448135</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.0274071811141844</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M4" t="n">
-        <v>122</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P4" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1167974844615735</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.05949724743333182</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -6769,40 +6766,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="AC4" t="n">
-        <v>44</v>
+        <v>-23</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1592309799362237</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.008537904728676542</v>
+        <v>0.001450929122771321</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03011243783512774</v>
+        <v>0.001964230860080685</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -6857,83 +6854,91 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43501</v>
+      </c>
+      <c r="M5" t="n">
+        <v>93</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1374122937580861</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1461625015373463</v>
+      </c>
+      <c r="P5" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.05008807998968798</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.02577413711690805</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>473</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="P5" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.2520853765532912</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.2520853765532912</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>-0.2551064931169149</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1374122937580861</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-50</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.47136484549988</v>
+        <v>0.1593024022528193</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.1840502243912828</v>
+        <v>-0.0001821148745050349</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>0.001911085271916746</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-8</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.145773903183348</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.1191788981215037</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6982,34 +6987,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43515</v>
+      </c>
+      <c r="M6" t="n">
+        <v>102</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1418618687233418</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1461625015373463</v>
+      </c>
+      <c r="P6" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.04822353288533004</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.02597547270868535</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44071</v>
-      </c>
-      <c r="M6" t="n">
-        <v>134</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="P6" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1410457549972917</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.07527274142776236</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7019,58 +7024,62 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1418618687233418</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="AC6" t="n">
-        <v>56</v>
+        <v>-41</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.47136484549988</v>
+        <v>0.1653135591496127</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.007237589265753991</v>
+        <v>1.922071727226277e-05</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>-0.00253848969333903</v>
       </c>
       <c r="AH6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.01577549399443053</v>
+        <v>-0.001431708405499058</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.03011243783512774</v>
+        <v>-0.004502720553419715</v>
       </c>
       <c r="AL6" t="n">
-        <v>12</v>
+        <v>-18</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.145773903183348</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>0.01662175333469529</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7115,34 +7124,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>43763</v>
+      </c>
+      <c r="M7" t="n">
+        <v>276</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1393233790300028</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1461625015373463</v>
+      </c>
+      <c r="P7" t="n">
+        <v>268</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.06395716047864553</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.05649563339197776</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44379</v>
-      </c>
-      <c r="M7" t="n">
-        <v>346</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="P7" t="n">
-        <v>345</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1957461336612948</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1674822394302119</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -7152,40 +7161,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>323</v>
+        <v>211</v>
       </c>
       <c r="AC7" t="n">
-        <v>268</v>
+        <v>133</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.47136484549988</v>
+        <v>0.1618765697074274</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.0994470872682035</v>
+        <v>0.03053938140056468</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7244,34 +7253,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43539</v>
+      </c>
+      <c r="M8" t="n">
+        <v>120</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1393233790300028</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1461625015373463</v>
+      </c>
+      <c r="P8" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.04909100017496723</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.02866027736808937</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44071</v>
-      </c>
-      <c r="M8" t="n">
-        <v>134</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="P8" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1410457549972917</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.07527274142776236</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -7281,52 +7290,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="AC8" t="n">
-        <v>56</v>
+        <v>-23</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.47136484549988</v>
+        <v>0.1618765697074274</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.007237589265753991</v>
+        <v>0.002704025376676286</v>
       </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.01577549399443053</v>
+        <v>0.001253096253904965</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.03011243783512774</v>
+        <v>-0.001964230860080685</v>
       </c>
       <c r="AL8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -7377,76 +7386,80 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>43763</v>
+      </c>
+      <c r="M9" t="n">
+        <v>276</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1393233790300028</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1461625015373464</v>
+      </c>
+      <c r="P9" t="n">
+        <v>268</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.06395716047864565</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.05649563339197787</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>473</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.3203589150179399</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.3203589150179399</v>
-      </c>
-      <c r="P9" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.2166718439219745</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.2166718439219745</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.1729699591525631</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3203589150179399</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3203589150179399</v>
+        <v>-0.1461625015373464</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>211</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>133</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4713648454998804</v>
+        <v>0.1618765697074274</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.1486366917599662</v>
+        <v>0.03053938140056479</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-2.220446049250313e-16</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>175</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -7502,34 +7515,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>43539</v>
+      </c>
+      <c r="M10" t="n">
+        <v>120</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1393233790300028</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1461625015373463</v>
+      </c>
+      <c r="P10" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.04909100017496723</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.02866027736808937</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44071</v>
-      </c>
-      <c r="M10" t="n">
-        <v>134</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="P10" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1410457549972917</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.07527274142776236</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -7539,52 +7552,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="AC10" t="n">
-        <v>56</v>
+        <v>-23</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.47136484549988</v>
+        <v>0.1618765697074274</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.007237589265753991</v>
+        <v>0.002704025376676286</v>
       </c>
       <c r="AG10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.01577549399443053</v>
+        <v>0.001253096253904965</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.03011243783512774</v>
+        <v>-0.001964230860080685</v>
       </c>
       <c r="AL10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -7887,34 +7900,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425155</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440421</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996986</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694572</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7924,22 +7937,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7948,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088533</v>
+        <v>0.4088864968986545</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -7996,34 +8009,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M3" t="n">
+        <v>122</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="P3" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1335580210897492</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06803515216200837</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45090</v>
-      </c>
-      <c r="M3" t="n">
-        <v>362</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3419503932402378</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3419503932402378</v>
-      </c>
-      <c r="P3" t="n">
-        <v>361</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2100698038590036</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1428506148817319</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8033,31 +8046,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="AC3" t="n">
-        <v>-55</v>
+        <v>44</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.5196422727520533</v>
+        <v>0.47136484549988</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8113,34 +8126,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M4" t="n">
+        <v>122</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P4" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1167974844615735</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05949724743333182</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45131</v>
-      </c>
-      <c r="M4" t="n">
-        <v>389</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="P4" t="n">
-        <v>388</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1306673287628706</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.09210103019783453</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -8150,40 +8163,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="AC4" t="n">
-        <v>-26</v>
+        <v>44</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3117521209239831</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0507495846838974</v>
+        <v>-0.008537904728676542</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1042895456218719</v>
+        <v>0.03011243783512774</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8238,91 +8251,83 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>473</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="P5" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.2520853765532912</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.2520853765532912</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45455</v>
-      </c>
-      <c r="M5" t="n">
-        <v>613</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.288215673541545</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2998248830871881</v>
-      </c>
-      <c r="P5" t="n">
-        <v>550</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.2064451437029497</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.1825803471265847</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>-0.2551064931169149</v>
+      </c>
       <c r="W5" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.288215673541545</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2998248830871881</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>416</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>196</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4049199495240183</v>
+        <v>0.47136484549988</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.03972973224485279</v>
+        <v>0.1840502243912828</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.05373471969869281</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>251</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.8578693937504649</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.4610239073873639</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8371,34 +8376,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44071</v>
+      </c>
+      <c r="M6" t="n">
+        <v>134</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="P6" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1410457549972917</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.07527274142776236</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45344</v>
-      </c>
-      <c r="M6" t="n">
-        <v>536</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3175486291732158</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3175486291732158</v>
-      </c>
-      <c r="P6" t="n">
-        <v>535</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1987128810730439</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1643532644258523</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -8408,62 +8413,58 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3175486291732158</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3175486291732158</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>339</v>
+        <v>111</v>
       </c>
       <c r="AC6" t="n">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.465305870495224</v>
+        <v>0.47136484549988</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.02150264954412034</v>
+        <v>0.007237589265753991</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.02440176406702199</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>174</v>
+        <v>12</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.07225223422801774</v>
+        <v>0.01577549399443053</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.07988778155484988</v>
+        <v>-0.03011243783512774</v>
       </c>
       <c r="AL6" t="n">
-        <v>145</v>
+        <v>12</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.8578693937504649</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.09630169010005585</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8508,34 +8509,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44379</v>
+      </c>
+      <c r="M7" t="n">
+        <v>346</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="P7" t="n">
+        <v>345</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1957461336612948</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.1674822394302119</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44628</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45064</v>
-      </c>
-      <c r="M7" t="n">
-        <v>345</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.1717629611374277</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.1717629611374277</v>
-      </c>
-      <c r="P7" t="n">
-        <v>344</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.07087649499468328</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.04705496487589172</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8545,40 +8546,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
-        <v>-151</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1717629611374277</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1717629611374277</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="AC7" t="n">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2073838201842697</v>
+        <v>0.47136484549988</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.0957956500058402</v>
+        <v>0.0994470872682035</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1701874321028101</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8637,34 +8638,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44071</v>
+      </c>
+      <c r="M8" t="n">
+        <v>134</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="P8" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1410457549972917</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.07527274142776236</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45091</v>
-      </c>
-      <c r="M8" t="n">
-        <v>363</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.265676705002627</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.265676705002627</v>
-      </c>
-      <c r="P8" t="n">
-        <v>362</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1643267387930042</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1118984574836809</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -8674,52 +8675,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.265676705002627</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.265676705002627</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="AC8" t="n">
-        <v>-52</v>
+        <v>56</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.3617980075159912</v>
+        <v>0.47136484549988</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.03095215739805106</v>
+        <v>0.007237589265753991</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.07627368823761083</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.01979742728584634</v>
+        <v>0.01577549399443053</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.02801585738426104</v>
+        <v>-0.03011243783512774</v>
       </c>
       <c r="AL8" t="n">
-        <v>-26</v>
+        <v>12</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -8770,87 +8771,83 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>513</v>
+        <v>473</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.00528167548620917</v>
+        <v>-0.3203589150179399</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.08987434123095583</v>
+        <v>-0.3203589150179399</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>473</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.01460551116785951</v>
+        <v>0.2166718439219745</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.2166718439219745</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
         <v>1</v>
       </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="n">
+        <v>-0.1729699591525631</v>
+      </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.00528167548620917</v>
+        <v>-0.3203589150179399</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.3203589150179399</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-220</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.4713648454998804</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1428506148817319</v>
+        <v>0.1486366917599662</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3366687177540286</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-165</v>
-      </c>
+        <v>-2.220446049250313e-16</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.1138279886626354</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-0.1020706911048278</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8899,34 +8896,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>44071</v>
+      </c>
+      <c r="M10" t="n">
+        <v>134</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="P10" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1410457549972917</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.07527274142776236</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45124</v>
-      </c>
-      <c r="M10" t="n">
-        <v>384</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="P10" t="n">
-        <v>383</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.131490457945522</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09208518698229826</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -8936,62 +8933,58 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>189</v>
+        <v>111</v>
       </c>
       <c r="AC10" t="n">
-        <v>-31</v>
+        <v>56</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.3117521209239831</v>
+        <v>0.47136484549988</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.05076542789943367</v>
+        <v>0.007237589265753991</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.1042895456218719</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>-1.584321553627088e-05</v>
+        <v>0.01577549399443053</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>0</v>
+        <v>-0.03011243783512774</v>
       </c>
       <c r="AL10" t="n">
-        <v>-5</v>
+        <v>12</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.1138279886626354</v>
-      </c>
-      <c r="AO10" s="3" t="n">
-        <v>-0.01271107771930213</v>
-      </c>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9288,34 +9281,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694572</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645815</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451831</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -9325,22 +9318,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -9349,7 +9342,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367012</v>
+        <v>0.4792042812088533</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -9397,34 +9390,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45090</v>
+      </c>
+      <c r="M3" t="n">
+        <v>362</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3419503932402378</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3419503932402378</v>
+      </c>
+      <c r="P3" t="n">
+        <v>361</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.2100698038590036</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1428506148817319</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45866</v>
-      </c>
-      <c r="M3" t="n">
-        <v>109</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.1938287231324922</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.1938287231324922</v>
-      </c>
-      <c r="P3" t="n">
-        <v>108</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.09021845436612216</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06408604615267784</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -9434,31 +9427,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="AC3" t="n">
-        <v>20</v>
+        <v>-55</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2404311945789499</v>
+        <v>0.5196422727520533</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -9514,34 +9507,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45131</v>
+      </c>
+      <c r="M4" t="n">
+        <v>389</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="P4" t="n">
+        <v>388</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1306673287628706</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09210103019783453</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M4" t="n">
-        <v>136</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P4" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.06348808787815403</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.05032969331821049</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -9551,40 +9544,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="AC4" t="n">
-        <v>47</v>
+        <v>-26</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.3117521209239831</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.01375635283446735</v>
+        <v>-0.0507495846838974</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.0397044101944054</v>
+        <v>0.1042895456218719</v>
       </c>
       <c r="AH4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9639,73 +9632,77 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45455</v>
+      </c>
+      <c r="M5" t="n">
+        <v>613</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.288215673541545</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2998248830871881</v>
+      </c>
+      <c r="P5" t="n">
+        <v>550</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.2064451437029497</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1825803471265847</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>88</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.288215673541545</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.2998248830871881</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>196</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.4049199495240183</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.06408604615267784</v>
+        <v>0.03972973224485279</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1938287231324922</v>
+        <v>0.05373471969869281</v>
       </c>
       <c r="AH5" t="n">
-        <v>-75</v>
+        <v>251</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9715,10 +9712,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.108636171448848</v>
+        <v>0.8578693937504649</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.08322383365112151</v>
+        <v>-0.4610239073873639</v>
       </c>
     </row>
     <row r="6">
@@ -9768,34 +9765,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="M6" t="n">
+        <v>536</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3175486291732158</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3175486291732158</v>
+      </c>
+      <c r="P6" t="n">
+        <v>535</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1987128810730439</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1643532644258523</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M6" t="n">
-        <v>136</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P6" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.06348808787815403</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.05032969331821049</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -9805,61 +9802,61 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3175486291732158</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3175486291732158</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>339</v>
       </c>
       <c r="AC6" t="n">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.465305870495224</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.01375635283446735</v>
+        <v>0.02150264954412034</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.0397044101944054</v>
+        <v>0.02440176406702199</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0</v>
+        <v>0.07225223422801774</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0</v>
+        <v>-0.07988778155484988</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.108636171448848</v>
+        <v>0.8578693937504649</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>0.0003678787044887333</v>
+        <v>-0.09630169010005585</v>
       </c>
     </row>
     <row r="7">
@@ -9905,73 +9902,77 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44628</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45064</v>
+      </c>
+      <c r="M7" t="n">
+        <v>345</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1717629611374277</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1717629611374277</v>
+      </c>
+      <c r="P7" t="n">
+        <v>344</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.07087649499468328</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.04705496487589172</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>88</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="X7" t="n">
-        <v>-34</v>
+        <v>-151</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1717629611374277</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1717629611374277</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="AC7" t="n">
-        <v>-55</v>
+        <v>81</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0</v>
+        <v>0.2073838201842697</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.06408604615267784</v>
+        <v>-0.0957956500058402</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1938287231324922</v>
+        <v>0.1701874321028101</v>
       </c>
       <c r="AH7" t="n">
-        <v>-75</v>
+        <v>136</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -9980,12 +9981,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.02421241003006935</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-0.01871188688585168</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10034,34 +10031,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45091</v>
+      </c>
+      <c r="M8" t="n">
+        <v>363</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.265676705002627</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.265676705002627</v>
+      </c>
+      <c r="P8" t="n">
+        <v>362</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1643267387930042</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.1118984574836809</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45866</v>
-      </c>
-      <c r="M8" t="n">
-        <v>109</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P8" t="n">
-        <v>108</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.06818954767041303</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.04843796681998232</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -10071,62 +10068,58 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.265676705002627</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.265676705002627</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="AC8" t="n">
-        <v>20</v>
+        <v>-52</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.3617980075159912</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.01564807933269551</v>
+        <v>-0.03095215739805106</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.0397044101944054</v>
+        <v>0.07627368823761083</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-0.001891726498228163</v>
+        <v>0.01979742728584634</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>0</v>
+        <v>-0.02801585738426104</v>
       </c>
       <c r="AL8" t="n">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
-      <c r="AN8" s="3" t="n">
-        <v>0.02421241003006935</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>0.04067970923593811</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10171,30 +10164,30 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>-0.00528167548620917</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>-0.08987434123095583</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>0.01460551116785951</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -10207,10 +10200,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.00528167548620917</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>0</v>
@@ -10222,7 +10215,7 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
@@ -10231,13 +10224,13 @@
         <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.06408604615267784</v>
+        <v>-0.1428506148817319</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1938287231324922</v>
+        <v>0.3366687177540286</v>
       </c>
       <c r="AH9" t="n">
-        <v>-75</v>
+        <v>-165</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10247,10 +10240,10 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="n">
-        <v>0.108636171448848</v>
+        <v>0.1138279886626354</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.08322383365112151</v>
+        <v>-0.1020706911048278</v>
       </c>
     </row>
     <row r="10">
@@ -10300,34 +10293,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45124</v>
+      </c>
+      <c r="M10" t="n">
+        <v>384</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="P10" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.131490457945522</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.09208518698229826</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45866</v>
-      </c>
-      <c r="M10" t="n">
-        <v>109</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P10" t="n">
-        <v>108</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.06818954767041303</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.04843796681998232</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -10337,61 +10330,61 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AC10" t="n">
-        <v>20</v>
+        <v>-31</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.3117521209239831</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.01564807933269551</v>
+        <v>-0.05076542789943367</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.0397044101944054</v>
+        <v>0.1042895456218719</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>-0.001891726498228163</v>
+        <v>-1.584321553627088e-05</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-27</v>
+        <v>-5</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.108636171448848</v>
+        <v>0.1138279886626354</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>0.0003678787044887333</v>
+        <v>-0.01271107771930213</v>
       </c>
     </row>
   </sheetData>
@@ -10405,7 +10398,1408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451831</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367012</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="M3" t="n">
+        <v>109</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1938287231324922</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1938287231324922</v>
+      </c>
+      <c r="P3" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.09021845436612216</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06408604615267784</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.1938287231324922</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.1938287231324922</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.2404311945789499</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M4" t="n">
+        <v>136</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P4" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.06348808787815403</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05032969331821049</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>34</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.01375635283446735</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.0397044101944054</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>89</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.06408604615267784</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.1938287231324922</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.108636171448848</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.08322383365112151</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M6" t="n">
+        <v>136</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P6" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06348808787815403</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.05032969331821049</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>34</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.01375635283446735</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.0397044101944054</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="3" t="n">
+        <v>0.108636171448848</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>0.0003678787044887333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>89</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.06408604615267784</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.1938287231324922</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.02421241003006935</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>-0.01871188688585168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="M8" t="n">
+        <v>109</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P8" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.06818954767041303</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.04843796681998232</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>34</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.01564807933269551</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.0397044101944054</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>-0.001891726498228163</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="3" t="n">
+        <v>0.02421241003006935</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>0.04067970923593811</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>89</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>-0.06408604615267784</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.1938287231324922</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.108636171448848</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.08322383365112151</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="M10" t="n">
+        <v>109</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P10" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.06818954767041303</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.04843796681998232</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>-0.01564807933269551</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0.0397044101944054</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>-0.001891726498228163</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AM10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3" t="n">
+        <v>0.108636171448848</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>0.0003678787044887333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10511,24 +11905,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>23</v>
+      </c>
       <c r="J2" s="3" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -10559,20 +11951,20 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-131</v>
+        <v>196</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.7281976744186046</v>
+        <v>0.473655019412091</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -10606,23 +11998,23 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-120</v>
+        <v>-131</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-57</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0.04137931034482759</v>
+        <v>0.7281976744186046</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -10652,19 +12044,21 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-57</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -10697,24 +12091,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-132</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>0.3625730994152047</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -10745,21 +12137,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-132</v>
+      </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -10776,37 +12170,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>259</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>59</v>
-      </c>
+        <v>-94</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0.1058171745152355</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -10833,27 +12225,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>0.3204941860465116</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -10880,25 +12270,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>59</v>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
+        <v>0.1059345535219079</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.4206896551724138</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -10925,25 +12317,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3204941860465116</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -10970,24 +12364,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>119</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -11017,27 +12409,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>58</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" s="3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -11054,24 +12444,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -11081,10 +12471,10 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>0.313573407202216</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -11101,37 +12491,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59</v>
+        <v>-30</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.4585755813953488</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -11158,25 +12548,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.4206896551724138</v>
-      </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -11203,25 +12595,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>183</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3139212423738214</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -11248,27 +12642,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-63</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.7309941520467836</v>
+        <v>0.4585755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -11295,32 +12689,169 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>58</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="3" t="n">
-        <v>1</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.7309941520467836</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-94</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>94</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
